--- a/data/trans_bre/IQ2608_R3-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IQ2608_R3-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,11</t>
+          <t>14,94</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 23,04</t>
+          <t>-7,45; 21,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 2,91</t>
+          <t>-23,0; 4,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,09; -1,03</t>
+          <t>-16,45; -1,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 40,51</t>
+          <t>-17,63; 41,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 44,53</t>
+          <t>-10,88; 42,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 3,98</t>
+          <t>-28,24; 6,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,6; -1,09</t>
+          <t>-16,96; -1,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 108,51</t>
+          <t>-26,66; 116,82</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,26</t>
+          <t>-13,24</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-11,78%</t>
+          <t>-25,46%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 7,69</t>
+          <t>-13,47; 8,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 16,68</t>
+          <t>-2,97; 16,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 12,11</t>
+          <t>-3,35; 12,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 24,54</t>
+          <t>-39,4; 11,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,71; 15,06</t>
+          <t>-21,63; 15,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 25,52</t>
+          <t>-4,01; 24,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 15,23</t>
+          <t>-3,7; 16,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,79; 68,62</t>
+          <t>-60,76; 36,41</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 16,19</t>
+          <t>-11,3; 15,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 9,46</t>
+          <t>-6,98; 8,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 6,0</t>
+          <t>-18,88; 3,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 26,66</t>
+          <t>-20,65; 28,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 43,9</t>
+          <t>-22,73; 44,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 11,09</t>
+          <t>-7,31; 10,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 7,84</t>
+          <t>-22,56; 5,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 49,35</t>
+          <t>-25,04; 54,87</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-48,79</t>
+          <t>-49,23</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-52,74%</t>
+          <t>-52,62%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 6,94</t>
+          <t>-19,94; 6,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 10,21</t>
+          <t>-12,85; 9,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 2,38</t>
+          <t>-16,84; 2,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,98; -20,02</t>
+          <t>-73,65; -18,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,74; 13,99</t>
+          <t>-32,86; 12,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 14,22</t>
+          <t>-15,58; 13,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 2,85</t>
+          <t>-18,56; 2,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,38; -24,27</t>
+          <t>-77,79; -23,56</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-25,53</t>
+          <t>-25,25</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-25,53%</t>
+          <t>-25,25%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 17,66</t>
+          <t>-15,75; 17,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 17,04</t>
+          <t>-10,63; 15,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 7,05</t>
+          <t>-9,81; 7,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-47,1; -8,55</t>
+          <t>-46,31; -10,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 32,5</t>
+          <t>-22,44; 31,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 23,86</t>
+          <t>-12,57; 22,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 7,89</t>
+          <t>-10,32; 8,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-47,1; -8,55</t>
+          <t>-46,31; -10,53</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-6,91</t>
+          <t>-5,87</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-9,74%</t>
+          <t>-8,44%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,28; -2,96</t>
+          <t>-32,44; -2,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 9,08</t>
+          <t>-7,44; 8,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 14,08</t>
+          <t>-15,44; 12,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,5; 21,76</t>
+          <t>-38,72; 22,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,61; -4,91</t>
+          <t>-42,13; -4,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 10,3</t>
+          <t>-7,78; 9,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 21,17</t>
+          <t>-19,3; 18,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 33,42</t>
+          <t>-49,08; 38,32</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-1,57</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-0,37%</t>
+          <t>-2,16%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 1,79</t>
+          <t>-17,24; 2,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 4,69</t>
+          <t>-10,15; 5,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 5,84</t>
+          <t>-11,27; 6,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 18,65</t>
+          <t>-21,78; 18,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 3,02</t>
+          <t>-27,07; 4,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 5,63</t>
+          <t>-11,38; 6,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 8,82</t>
+          <t>-14,96; 10,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 28,44</t>
+          <t>-27,05; 29,13</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>8,02</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 6,47</t>
+          <t>-7,23; 6,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 3,79</t>
+          <t>-10,98; 3,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 3,28</t>
+          <t>-9,06; 3,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 22,89</t>
+          <t>-12,03; 26,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 8,26</t>
+          <t>-8,52; 8,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 4,87</t>
+          <t>-12,6; 4,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 3,88</t>
+          <t>-10,11; 3,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 39,58</t>
+          <t>-15,17; 49,64</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-4,52</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-5,72%</t>
+          <t>-6,6%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 1,13</t>
+          <t>-7,08; 1,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 2,17</t>
+          <t>-4,14; 2,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 0,6</t>
+          <t>-6,31; 0,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 4,82</t>
+          <t>-13,67; 5,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 1,76</t>
+          <t>-10,84; 1,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 2,67</t>
+          <t>-4,98; 3,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 0,68</t>
+          <t>-7,37; 0,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 7,66</t>
+          <t>-18,85; 7,91</t>
         </is>
       </c>
     </row>
